--- a/Synapse_Project_Plan_v3.xlsx
+++ b/Synapse_Project_Plan_v3.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint Plan" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks &amp; Decisions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Plan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Milestones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sprint Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Risks &amp; Decisions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -655,7 +655,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -1114,11 +1114,11 @@
       </c>
       <c r="G2" s="14" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H2" s="16" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="I2" s="17" t="n">
         <v>46160</v>
@@ -1126,14 +1126,16 @@
       <c r="J2" s="17" t="n">
         <v>46171</v>
       </c>
-      <c r="K2" s="17" t="n"/>
+      <c r="K2" s="17" t="n">
+        <v>46176</v>
+      </c>
       <c r="L2" s="14">
         <f>IF(K2="","",IF(K2&lt;=J2,"On-Time","Late"))</f>
         <v/>
       </c>
       <c r="M2" s="15" t="inlineStr">
         <is>
-          <t>Team began 18 May. Immutable envelope, idempotency key.</t>
+          <t>COMPLETE (T-01) — immutable envelope + SHA-256 checksum existed; added hub/topic.ts (canonical source.entity.event, validate/parse/build, centralized topicMatches), topic validation + idempotency-key-derived messageId in createEnvelope, router refactor. 59 hub tests pass.</t>
         </is>
       </c>
     </row>
@@ -1386,11 +1388,11 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H7" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="17" t="n">
         <v>46160</v>
@@ -1398,14 +1400,16 @@
       <c r="J7" s="17" t="n">
         <v>46171</v>
       </c>
-      <c r="K7" s="17" t="n"/>
+      <c r="K7" s="17" t="n">
+        <v>46175</v>
+      </c>
       <c r="L7" s="14">
         <f>IF(K7="","",IF(K7&lt;=J7,"On-Time","Late"))</f>
         <v/>
       </c>
       <c r="M7" s="15" t="inlineStr">
         <is>
-          <t>Reuse SP source + type mapper.</t>
+          <t>COMPLETE (T-06) — SqlServerWriter smartUpsert + sys.columns introspect + hub MSSQL endpoints + wizard wiring. Tested.</t>
         </is>
       </c>
     </row>
@@ -1440,11 +1444,11 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H8" s="16" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I8" s="17" t="n">
         <v>46160</v>
@@ -1459,7 +1463,7 @@
       </c>
       <c r="M8" s="15" t="inlineStr">
         <is>
-          <t>First real-data screens.</t>
+          <t>T-07 code-complete: integrationMap.js shared mapper, live KPIs/tiles/charts off /api/connected, sample fallback, 0 diagnostics. Pending browser verify for M1.</t>
         </is>
       </c>
     </row>

--- a/Synapse_Project_Plan_v3.xlsx
+++ b/Synapse_Project_Plan_v3.xlsx
@@ -1170,11 +1170,11 @@
       </c>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H3" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="17" t="n">
         <v>46160</v>
@@ -1182,14 +1182,16 @@
       <c r="J3" s="17" t="n">
         <v>46171</v>
       </c>
-      <c r="K3" s="17" t="n"/>
+      <c r="K3" s="17" t="n">
+        <v>46176</v>
+      </c>
       <c r="L3" s="14">
         <f>IF(K3="","",IF(K3&lt;=J3,"On-Time","Late"))</f>
         <v/>
       </c>
       <c r="M3" s="15" t="inlineStr">
         <is>
-          <t>Backpressure via bounded queue.</t>
+          <t>COMPLETE (T-02, direction A) — SubscriptionRegistry (org-scoped findMatching), BoundedQueue (FIFO + backpressure), InMemoryBus (publish-&gt;queue-&gt;router fan-out, checksum-validate, transform hook). 76 hub tests pass.</t>
         </is>
       </c>
     </row>
@@ -1224,11 +1226,11 @@
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H4" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="17" t="n">
         <v>46160</v>
@@ -1236,14 +1238,16 @@
       <c r="J4" s="17" t="n">
         <v>46171</v>
       </c>
-      <c r="K4" s="17" t="n"/>
+      <c r="K4" s="17" t="n">
+        <v>46176</v>
+      </c>
       <c r="L4" s="14">
         <f>IF(K4="","",IF(K4&lt;=J4,"On-Time","Late"))</f>
         <v/>
       </c>
       <c r="M4" s="15" t="inlineStr">
         <is>
-          <t>LLD §8 schema, Drizzle.</t>
+          <t>COMPLETE (T-03) — 4 Drizzle tables + repos existed; added hub/durable-bus.ts orchestrating store-and-forward (inbox checkpoint -&gt; idempotency dedup -&gt; outbox -&gt; dispatch -&gt; markDone/dead-letter) over T-02 fan-out, + createDurablePorts factory. 85 hub tests pass.</t>
         </is>
       </c>
     </row>
@@ -1278,11 +1282,11 @@
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H5" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="17" t="n">
         <v>46160</v>
@@ -1290,14 +1294,16 @@
       <c r="J5" s="17" t="n">
         <v>46171</v>
       </c>
-      <c r="K5" s="17" t="n"/>
+      <c r="K5" s="17" t="n">
+        <v>46176</v>
+      </c>
       <c r="L5" s="14">
         <f>IF(K5="","",IF(K5&lt;=J5,"On-Time","Late"))</f>
         <v/>
       </c>
       <c r="M5" s="15" t="inlineStr">
         <is>
-          <t>Per Architecture §11.</t>
+          <t>COMPLETE (T-04) — hub/retry.ts (exp backoff + jitter, withRetry), hub/circuit-breaker.ts (closed/open/half-open), hub/dlq-replay-service.ts (auto+manual replay -&gt; resolve/retry/poison); retry+per-dest breaker wired into DurableBus (opt-in). 100 hub tests pass.</t>
         </is>
       </c>
     </row>
@@ -1444,11 +1450,11 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H8" s="16" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="I8" s="17" t="n">
         <v>46160</v>
@@ -1456,14 +1462,16 @@
       <c r="J8" s="17" t="n">
         <v>46171</v>
       </c>
-      <c r="K8" s="17" t="n"/>
+      <c r="K8" s="17" t="n">
+        <v>46176</v>
+      </c>
       <c r="L8" s="14">
         <f>IF(K8="","",IF(K8&lt;=J8,"On-Time","Late"))</f>
         <v/>
       </c>
       <c r="M8" s="15" t="inlineStr">
         <is>
-          <t>T-07 code-complete: integrationMap.js shared mapper, live KPIs/tiles/charts off /api/connected, sample fallback, 0 diagnostics. Pending browser verify for M1.</t>
+          <t>COMPLETE (T-07) — integrationMap.js shared mapper, live KPIs/tiles/charts off /api/connected, sample fallback, 0 diagnostics. Browser-verified headless (verify-t07.mjs): Dashboard + Registry render the 'Live' badge with real adapters (SP-&gt;SQL Server, SP-&gt;MySQL).</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3046,7 @@
       </c>
       <c r="D2" s="14" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Achieved</t>
         </is>
       </c>
       <c r="E2" s="14" t="inlineStr">
@@ -3051,7 +3059,9 @@
           <t>Message flows Inbox-&gt;Bus-&gt;Router-&gt;Outbox; DLQ on forced failure; SP-&gt;PG + SP-&gt;MSSQL write live; Dashboard &amp; Registry show real runs.</t>
         </is>
       </c>
-      <c r="G2" s="17" t="n"/>
+      <c r="G2" s="17" t="n">
+        <v>46176</v>
+      </c>
       <c r="H2" s="14">
         <f>IF(G2="","",NETWORKDAYS(C2,G2)-1)</f>
         <v/>

--- a/Synapse_Project_Plan_v3.xlsx
+++ b/Synapse_Project_Plan_v3.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H9" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="17" t="n">
         <v>46174</v>
@@ -1518,14 +1518,16 @@
       <c r="J9" s="17" t="n">
         <v>46185</v>
       </c>
-      <c r="K9" s="17" t="n"/>
+      <c r="K9" s="17" t="n">
+        <v>46177</v>
+      </c>
       <c r="L9" s="14">
         <f>IF(K9="","",IF(K9&lt;=J9,"On-Time","Late"))</f>
         <v/>
       </c>
       <c r="M9" s="15" t="inlineStr">
         <is>
-          <t>Hard test-before-publish gate.</t>
+          <t>COMPLETE (T-08) — Wizard cut over to the connector registry: removed all hardcoded source/dest cards, per-system credential schemas and DB engine config; now loads cards + credential-schema + runtime-config + entities from /api/connectors. Generic-REST and SharePoint-by-runtimeKind source branches (test/entities/fields/fetch/push); REST-&gt;DB and REST-&gt;REST push; Step-4 'Edit in Mapping Canvas' handoff; persists sourceConnectorId/destConnectorId + version pins. Builds clean.</t>
         </is>
       </c>
     </row>
@@ -1560,11 +1562,11 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H10" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="17" t="n">
         <v>46174</v>
@@ -1572,14 +1574,16 @@
       <c r="J10" s="17" t="n">
         <v>46185</v>
       </c>
-      <c r="K10" s="17" t="n"/>
+      <c r="K10" s="17" t="n">
+        <v>46177</v>
+      </c>
       <c r="L10" s="14">
         <f>IF(K10="","",IF(K10&lt;=J10,"On-Time","Late"))</f>
         <v/>
       </c>
       <c r="M10" s="15" t="inlineStr">
         <is>
-          <t>Human-confirm required.</t>
+          <t>COMPLETE (T-09) — shared components/mapping module; MappingAIService (Claude auto-map + NL-&gt;JS transform, deterministic fallback, ANTHROPIC_API_KEY optional); GET/PUT /api/integrations/:id/mappings + /auto-map + /transform/nl; Canvas rewritten as a real editor (integration picker, AI auto-map w/ confidence colours, editable transforms + live preview, persist); Wizard-&gt;Canvas handoff. Verified.</t>
         </is>
       </c>
     </row>
@@ -1830,11 +1834,11 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H15" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="17" t="n">
         <v>46188</v>
@@ -1842,14 +1846,16 @@
       <c r="J15" s="17" t="n">
         <v>46199</v>
       </c>
-      <c r="K15" s="17" t="n"/>
+      <c r="K15" s="17" t="n">
+        <v>46177</v>
+      </c>
       <c r="L15" s="14">
         <f>IF(K15="","",IF(K15&lt;=J15,"On-Time","Late"))</f>
         <v/>
       </c>
       <c r="M15" s="15" t="inlineStr">
         <is>
-          <t>Designer workflow.</t>
+          <t>COMPLETE (T-14) — connector registry (connectors/versions/operations/entity tables + seed of 5 built-ins) + ConnectorService; Studio backend: CRUD + draft/publish versioning + publish test-gate; OpenAPI 3.0 parser; DB-introspect + generic database template (no design-time connection, Docker-image model); SharePoint runtime preset; clone; generic REST runtime (auth apiKey/bearer/basic/oauth2-cc + fetch/push + REST-&gt;DB write). Studio BRD 5-stage authoring UI: System Registration -&gt; Authentication -&gt; Operation Selection (R/W/Both + hide-from-Operator) -&gt; Entity Modelling (Master-Catalog link) -&gt; Publish &amp; Version (sample-cred test gate). 414 backend tests pass.</t>
         </is>
       </c>
     </row>
@@ -2100,11 +2106,11 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H20" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="17" t="n">
         <v>46202</v>
@@ -2112,14 +2118,16 @@
       <c r="J20" s="17" t="n">
         <v>46213</v>
       </c>
-      <c r="K20" s="17" t="n"/>
+      <c r="K20" s="17" t="n">
+        <v>46177</v>
+      </c>
       <c r="L20" s="14">
         <f>IF(K20="","",IF(K20&lt;=J20,"On-Time","Late"))</f>
         <v/>
       </c>
       <c r="M20" s="15" t="inlineStr">
         <is>
-          <t>Cross-adapter reference.</t>
+          <t>COMPLETE (T-19) — GET /api/entities aggregates entities per connector + field-level usage counts (from integrations.fieldMappings.mappings) + used-by-adapters; CatalogPage rewritten: connector-&gt;entity tree, field/type/usage table, cross-refs to Studio/Registry; entity-&gt;Master-Catalog link surfaced (entity_definitions.master_entity_key). Verified.</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3091,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Achieved</t>
         </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
@@ -3096,7 +3104,9 @@
           <t>Operator builds an integration through all 6 steps; AI auto-map suggests with confidence; test-before-publish gate enforced.</t>
         </is>
       </c>
-      <c r="G3" s="17" t="n"/>
+      <c r="G3" s="17" t="n">
+        <v>46177</v>
+      </c>
       <c r="H3" s="14">
         <f>IF(G3="","",NETWORKDAYS(C3,G3)-1)</f>
         <v/>

--- a/Synapse_Project_Plan_v3.xlsx
+++ b/Synapse_Project_Plan_v3.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1519,7 +1519,7 @@
         <v>46185</v>
       </c>
       <c r="K9" s="17" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="L9" s="14">
         <f>IF(K9="","",IF(K9&lt;=J9,"On-Time","Late"))</f>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="M9" s="15" t="inlineStr">
         <is>
-          <t>COMPLETE (T-08) — Wizard cut over to the connector registry: removed all hardcoded source/dest cards, per-system credential schemas and DB engine config; now loads cards + credential-schema + runtime-config + entities from /api/connectors. Generic-REST and SharePoint-by-runtimeKind source branches (test/entities/fields/fetch/push); REST-&gt;DB and REST-&gt;REST push; Step-4 'Edit in Mapping Canvas' handoff; persists sourceConnectorId/destConnectorId + version pins. Builds clean.</t>
+          <t>COMPLETE (T-08, hardened) — registry-driven 6-step wizard cut over to a runtimeClient facade: generic /api/connectors/runtime/* dispatch by runtimeKind (NOT display-label -&gt; fixes cloned-connector misroute); works for all 12 categories. Step-4: real existing-table columns vs derive-on-create, schema evolution (ALTER ADD missing cols), object-&gt;JSON coercion, empty-string-&gt;NULL, selectable Match/dedup key (or append), always-on auto-PK on new tables, Flat-File upload control, surfaces push errors; Canvas handoff + resume. Persists source/dest connector + version pins.</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>Wire Monitor + Connected + Push to real APIs</t>
+          <t>Wire Monitor + Connected + Push to real APIs (remove ALL mock data)</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -1672,11 +1672,11 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H12" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="17" t="n">
         <v>46174</v>
@@ -1684,14 +1684,16 @@
       <c r="J12" s="17" t="n">
         <v>46185</v>
       </c>
-      <c r="K12" s="17" t="n"/>
+      <c r="K12" s="17" t="n">
+        <v>46178</v>
+      </c>
       <c r="L12" s="14">
         <f>IF(K12="","",IF(K12&lt;=J12,"On-Time","Late"))</f>
         <v/>
       </c>
       <c r="M12" s="15" t="inlineStr">
         <is>
-          <t>Replace remaining mocks.</t>
+          <t>COMPLETE (T-11) — deleted all 8 mock data files + fallbacks app-wide: Registry/Dashboard/Connected drop the sample fallback (real-or-empty), Monitor run-history -&gt; empty state (real DLQ panel kept; seed/echo demo removed), Alerts -&gt; real /api/alerts, Admin users/clients -&gt; empty, Topbar global search indexes real connectors/connections/entities. Every page shows real backend data or an honest empty state.</t>
         </is>
       </c>
     </row>
@@ -1726,11 +1728,11 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H13" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="17" t="n">
         <v>46174</v>
@@ -1738,14 +1740,16 @@
       <c r="J13" s="17" t="n">
         <v>46185</v>
       </c>
-      <c r="K13" s="17" t="n"/>
+      <c r="K13" s="17" t="n">
+        <v>46178</v>
+      </c>
       <c r="L13" s="14">
         <f>IF(K13="","",IF(K13&lt;=J13,"On-Time","Late"))</f>
         <v/>
       </c>
       <c r="M13" s="15" t="inlineStr">
         <is>
-          <t>AES-256-GCM in place.</t>
+          <t>COMPLETE (T-12) — VaultPage rewritten onto real /api/credentials (metadata list) + decrypt-on-reveal via /api/credentials/:id/decrypt (10s auto-hide); DB-connection credential form (test + save, AES-256-GCM). No mock keys/owners.</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1851,7 @@
         <v>46199</v>
       </c>
       <c r="K15" s="17" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="L15" s="14">
         <f>IF(K15="","",IF(K15&lt;=J15,"On-Time","Late"))</f>
@@ -1855,7 +1859,7 @@
       </c>
       <c r="M15" s="15" t="inlineStr">
         <is>
-          <t>COMPLETE (T-14) — connector registry (connectors/versions/operations/entity tables + seed of 5 built-ins) + ConnectorService; Studio backend: CRUD + draft/publish versioning + publish test-gate; OpenAPI 3.0 parser; DB-introspect + generic database template (no design-time connection, Docker-image model); SharePoint runtime preset; clone; generic REST runtime (auth apiKey/bearer/basic/oauth2-cc + fetch/push + REST-&gt;DB write). Studio BRD 5-stage authoring UI: System Registration -&gt; Authentication -&gt; Operation Selection (R/W/Both + hide-from-Operator) -&gt; Entity Modelling (Master-Catalog link) -&gt; Publish &amp; Version (sample-cred test gate). 414 backend tests pass.</t>
+          <t>COMPLETE (T-14, expanded to full FSD) — data-driven Studio: backend CATEGORY_REGISTRY (12 categories, per-category auth+config from FSD §4/§5) + runtime registry (IConnectorRuntime + capabilities). StudioPage rebuilt: 6-stage flow (System Reg -&gt; Authentication -&gt; Operation Selection[R/W/Both + hide-from-Operator] -&gt; Entity Modelling[rename/canonical-type/PK natural-key/Master-Catalog link] -&gt; Test &amp; Validate -&gt; Publish &amp; Version) + versioning (rollback/deprecate/sunset + connector_test_runs gate) + clone + force-delete. OpenAPI parser, DB-introspect/Docker-image template, SP preset. 432 backend tests pass.</t>
         </is>
       </c>
     </row>
@@ -1944,11 +1948,11 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H17" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="17" t="n">
         <v>46188</v>
@@ -1956,14 +1960,16 @@
       <c r="J17" s="17" t="n">
         <v>46199</v>
       </c>
-      <c r="K17" s="17" t="n"/>
+      <c r="K17" s="17" t="n">
+        <v>46178</v>
+      </c>
       <c r="L17" s="14">
         <f>IF(K17="","",IF(K17&lt;=J17,"On-Time","Late"))</f>
         <v/>
       </c>
       <c r="M17" s="15" t="inlineStr">
         <is>
-          <t>Replace hardcoded SVG.</t>
+          <t>COMPLETE (T-16) — Dashboard KPIs (total/active/paused/errored, records synced, push ok/partial/failed, success rate, alerts) + volume/error MiniBars computed live from /api/connected + push history; removed sample tiles + hardcoded numbers. Empty-safe (zeros when no data).</t>
         </is>
       </c>
     </row>
@@ -2144,29 +2150,29 @@
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Connectors</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>Multi-tenancy / org enforcement (row-level org_id, integrated with Policy)</t>
+          <t>12-category connector platform — runtime registry + 8 new runtimes (GraphQL / Flat File / Webhook / Message Queue / File Share / SOAP / Web Scraping / Email)</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>Dev A</t>
+          <t>Dev B</t>
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H21" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="17" t="n">
         <v>46202</v>
@@ -2174,14 +2180,16 @@
       <c r="J21" s="17" t="n">
         <v>46213</v>
       </c>
-      <c r="K21" s="17" t="n"/>
+      <c r="K21" s="17" t="n">
+        <v>46178</v>
+      </c>
       <c r="L21" s="14">
         <f>IF(K21="","",IF(K21&lt;=J21,"On-Time","Late"))</f>
         <v/>
       </c>
       <c r="M21" s="15" t="inlineStr">
         <is>
-          <t>Data isolation.</t>
+          <t>COMPLETE — IConnectorRuntime + capabilities; every category is authorable AND moves data. Verified live: GraphQL 250 rec, CSV/XLSX parse, SFTP listing (test.rebex.net), SOAP Add=12, Playwright scrape example.com, Webhook ingest-&gt;drain (hub inbox, first prod use), Redis-Streams peek, DB auto-create+upsert. Heavy deps lazy-imported (csv-parse, xlsx, ssh2-sftp-client, strong-soap, imapflow).</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2206,17 @@
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Scheduler</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>Scheduler wire + cron builder UI (BullMQ repeatable jobs)</t>
+          <t>Multi-tenancy / org enforcement (row-level org_id, integrated with Policy)</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Dev B</t>
+          <t>Dev A</t>
         </is>
       </c>
       <c r="F22" s="14" t="n">
@@ -2235,7 +2243,7 @@
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
-          <t>Next-run preview.</t>
+          <t>Data isolation.</t>
         </is>
       </c>
     </row>
@@ -2252,12 +2260,12 @@
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Adapter</t>
+          <t>Scheduler</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>Jira -&gt; SharePoint parity verify + harden</t>
+          <t>Scheduler wire + cron builder UI (BullMQ repeatable jobs)</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -2266,7 +2274,7 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
@@ -2289,7 +2297,7 @@
       </c>
       <c r="M23" s="15" t="inlineStr">
         <is>
-          <t>Existing engine regression.</t>
+          <t>Next-run preview.</t>
         </is>
       </c>
     </row>
@@ -2306,21 +2314,21 @@
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Adapter</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>End-to-end integration testing + bug bash (all modules)</t>
+          <t>Jira -&gt; SharePoint parity verify + harden</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Dev B</t>
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -2343,7 +2351,7 @@
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
-          <t>Feature-complete gate.</t>
+          <t>Existing engine regression.</t>
         </is>
       </c>
     </row>
@@ -2355,17 +2363,17 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Stab</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Hardening</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>Security review (vault, policy enforcement, OWASP) + perf test (parallel workers)</t>
+          <t>End-to-end integration testing + bug bash (all modules)</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
@@ -2374,7 +2382,7 @@
         </is>
       </c>
       <c r="F25" s="14" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -2385,10 +2393,10 @@
         <v>0</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>46216</v>
+        <v>46202</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>46220</v>
+        <v>46213</v>
       </c>
       <c r="K25" s="17" t="n"/>
       <c r="L25" s="14">
@@ -2397,7 +2405,7 @@
       </c>
       <c r="M25" s="15" t="inlineStr">
         <is>
-          <t>Pre-UAT gate.</t>
+          <t>Feature-complete gate.</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2427,7 @@
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>Regression suite + smoke + fixes</t>
+          <t>Security review (vault, policy enforcement, OWASP) + perf test (parallel workers)</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
@@ -2428,7 +2436,7 @@
         </is>
       </c>
       <c r="F26" s="14" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -2451,7 +2459,7 @@
       </c>
       <c r="M26" s="15" t="inlineStr">
         <is>
-          <t>Stabilize.</t>
+          <t>Pre-UAT gate.</t>
         </is>
       </c>
     </row>
@@ -2468,21 +2476,21 @@
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Deploy</t>
+          <t>Hardening</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>Deploy to UAT environment (Docker) + smoke + runbook</t>
+          <t>Regression suite + smoke + fixes</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>Dev A</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
@@ -2505,7 +2513,7 @@
       </c>
       <c r="M27" s="15" t="inlineStr">
         <is>
-          <t>Code freeze.</t>
+          <t>Stabilize.</t>
         </is>
       </c>
     </row>
@@ -2517,26 +2525,26 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>UAT</t>
+          <t>Stab</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>UAT</t>
+          <t>Deploy</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>UAT planning + scenarios + test-data setup</t>
+          <t>Deploy to UAT environment (Docker) + smoke + runbook</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>BA/QA</t>
+          <t>Dev A</t>
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
@@ -2547,10 +2555,10 @@
         <v>0</v>
       </c>
       <c r="I28" s="17" t="n">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="J28" s="17" t="n">
-        <v>46248</v>
+        <v>46220</v>
       </c>
       <c r="K28" s="17" t="n"/>
       <c r="L28" s="14">
@@ -2559,7 +2567,7 @@
       </c>
       <c r="M28" s="15" t="inlineStr">
         <is>
-          <t>Scripts per module.</t>
+          <t>Code freeze.</t>
         </is>
       </c>
     </row>
@@ -2581,16 +2589,16 @@
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>UAT cycle 1 execution</t>
+          <t>UAT planning + scenarios + test-data setup</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>QA + Stakeholders</t>
+          <t>BA/QA</t>
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
@@ -2613,7 +2621,7 @@
       </c>
       <c r="M29" s="15" t="inlineStr">
         <is>
-          <t>Log defects.</t>
+          <t>Scripts per module.</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2643,12 @@
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>Defect triage + fixes (cycle 1)</t>
+          <t>UAT cycle 1 execution</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>QA + Stakeholders</t>
         </is>
       </c>
       <c r="F30" s="14" t="n">
@@ -2667,7 +2675,7 @@
       </c>
       <c r="M30" s="15" t="inlineStr">
         <is>
-          <t>Devs on standby.</t>
+          <t>Log defects.</t>
         </is>
       </c>
     </row>
@@ -2689,16 +2697,16 @@
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>UAT cycle 2 + regression</t>
+          <t>Defect triage + fixes (cycle 1)</t>
         </is>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
@@ -2721,7 +2729,7 @@
       </c>
       <c r="M31" s="15" t="inlineStr">
         <is>
-          <t>Verify fixes.</t>
+          <t>Devs on standby.</t>
         </is>
       </c>
     </row>
@@ -2743,16 +2751,16 @@
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>UAT signoff + go-live readiness</t>
+          <t>UAT cycle 2 + regression</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>BA + Stakeholders</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2775,44 +2783,76 @@
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
+          <t>Verify fixes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>T-32</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>UAT</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>UAT</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>UAT signoff + go-live readiness</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>BA + Stakeholders</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="17" t="n">
+        <v>46223</v>
+      </c>
+      <c r="J33" s="17" t="n">
+        <v>46248</v>
+      </c>
+      <c r="K33" s="17" t="n"/>
+      <c r="L33" s="14">
+        <f>IF(K33="","",IF(K33&lt;=J33,"On-Time","Late"))</f>
+        <v/>
+      </c>
+      <c r="M33" s="15" t="inlineStr">
+        <is>
           <t>Final acceptance.</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="n"/>
-      <c r="B33" s="18" t="n"/>
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>S1 subtotal</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="n"/>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="20">
-        <f>SUM(F2:F8)</f>
-        <v/>
-      </c>
-      <c r="G33" s="18" t="n"/>
-      <c r="H33" s="18" t="n"/>
-      <c r="I33" s="18" t="n"/>
-      <c r="J33" s="18" t="n"/>
-      <c r="K33" s="18" t="n"/>
-      <c r="L33" s="18" t="n"/>
-      <c r="M33" s="18" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="18" t="n"/>
       <c r="B34" s="18" t="n"/>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>S2 subtotal</t>
+          <t>S1 subtotal</t>
         </is>
       </c>
       <c r="D34" s="18" t="n"/>
       <c r="E34" s="18" t="n"/>
       <c r="F34" s="20">
-        <f>SUM(F9:F13)</f>
+        <f>SUM(F2:F8)</f>
         <v/>
       </c>
       <c r="G34" s="18" t="n"/>
@@ -2828,13 +2868,13 @@
       <c r="B35" s="18" t="n"/>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t>S3 subtotal</t>
+          <t>S2 subtotal</t>
         </is>
       </c>
       <c r="D35" s="18" t="n"/>
       <c r="E35" s="18" t="n"/>
       <c r="F35" s="20">
-        <f>SUM(F14:F18)</f>
+        <f>SUM(F9:F13)</f>
         <v/>
       </c>
       <c r="G35" s="18" t="n"/>
@@ -2850,13 +2890,13 @@
       <c r="B36" s="18" t="n"/>
       <c r="C36" s="19" t="inlineStr">
         <is>
-          <t>S4 subtotal</t>
+          <t>S3 subtotal</t>
         </is>
       </c>
       <c r="D36" s="18" t="n"/>
       <c r="E36" s="18" t="n"/>
       <c r="F36" s="20">
-        <f>SUM(F19:F24)</f>
+        <f>SUM(F14:F18)</f>
         <v/>
       </c>
       <c r="G36" s="18" t="n"/>
@@ -2872,13 +2912,13 @@
       <c r="B37" s="18" t="n"/>
       <c r="C37" s="19" t="inlineStr">
         <is>
-          <t>Stab subtotal</t>
+          <t>S4 subtotal</t>
         </is>
       </c>
       <c r="D37" s="18" t="n"/>
       <c r="E37" s="18" t="n"/>
       <c r="F37" s="20">
-        <f>SUM(F25:F27)</f>
+        <f>SUM(F19:F25)</f>
         <v/>
       </c>
       <c r="G37" s="18" t="n"/>
@@ -2894,13 +2934,13 @@
       <c r="B38" s="18" t="n"/>
       <c r="C38" s="19" t="inlineStr">
         <is>
-          <t>UAT subtotal</t>
+          <t>Stab subtotal</t>
         </is>
       </c>
       <c r="D38" s="18" t="n"/>
       <c r="E38" s="18" t="n"/>
       <c r="F38" s="20">
-        <f>SUM(F28:F32)</f>
+        <f>SUM(F26:F28)</f>
         <v/>
       </c>
       <c r="G38" s="18" t="n"/>
@@ -2912,29 +2952,51 @@
       <c r="M38" s="18" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="21" t="n"/>
-      <c r="B39" s="21" t="n"/>
-      <c r="C39" s="21" t="inlineStr">
+      <c r="A39" s="18" t="n"/>
+      <c r="B39" s="18" t="n"/>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>UAT subtotal</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="20">
+        <f>SUM(F29:F33)</f>
+        <v/>
+      </c>
+      <c r="G39" s="18" t="n"/>
+      <c r="H39" s="18" t="n"/>
+      <c r="I39" s="18" t="n"/>
+      <c r="J39" s="18" t="n"/>
+      <c r="K39" s="18" t="n"/>
+      <c r="L39" s="18" t="n"/>
+      <c r="M39" s="18" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="n"/>
+      <c r="B40" s="21" t="n"/>
+      <c r="C40" s="21" t="inlineStr">
         <is>
           <t>GRAND TOTAL (hrs)</t>
         </is>
       </c>
-      <c r="D39" s="21" t="n"/>
-      <c r="E39" s="21" t="n"/>
-      <c r="F39" s="22">
-        <f>SUM(F2:F32)</f>
-        <v/>
-      </c>
-      <c r="G39" s="21" t="n"/>
-      <c r="H39" s="21" t="n"/>
-      <c r="I39" s="21" t="n"/>
-      <c r="J39" s="21" t="n"/>
-      <c r="K39" s="21" t="n"/>
-      <c r="L39" s="21" t="n"/>
-      <c r="M39" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="22">
+        <f>SUM(F2:F33)</f>
+        <v/>
+      </c>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="21" t="n"/>
+      <c r="I40" s="21" t="n"/>
+      <c r="J40" s="21" t="n"/>
+      <c r="K40" s="21" t="n"/>
+      <c r="L40" s="21" t="n"/>
+      <c r="M40" s="21" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:G32">
+  <conditionalFormatting sqref="G2:G33">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Not Started"</formula>
     </cfRule>
@@ -2948,7 +3010,7 @@
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L32">
+  <conditionalFormatting sqref="L2:L33">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
       <formula>"On-Time"</formula>
     </cfRule>
@@ -2956,7 +3018,7 @@
       <formula>"Late"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H32">
+  <conditionalFormatting sqref="H2:H33">
     <cfRule type="dataBar" priority="7">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -2966,10 +3028,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="G2:G32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not Started,In Progress,Blocked,Done"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"0,0.25,0.5,0.75,1"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3361,7 +3423,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="24">
-        <f>SUMIFS(Plan!F2:F32,Plan!B2:B32,A2)</f>
+        <f>SUMIFS(Plan!F2:F33,Plan!B2:B33,A2)</f>
         <v/>
       </c>
       <c r="G2" s="25">
@@ -3395,7 +3457,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="24">
-        <f>SUMIFS(Plan!F2:F32,Plan!B2:B32,A3)</f>
+        <f>SUMIFS(Plan!F2:F33,Plan!B2:B33,A3)</f>
         <v/>
       </c>
       <c r="G3" s="25">
@@ -3429,7 +3491,7 @@
         <v>144</v>
       </c>
       <c r="F4" s="24">
-        <f>SUMIFS(Plan!F2:F32,Plan!B2:B32,A4)</f>
+        <f>SUMIFS(Plan!F2:F33,Plan!B2:B33,A4)</f>
         <v/>
       </c>
       <c r="G4" s="25">
@@ -3463,7 +3525,7 @@
         <v>144</v>
       </c>
       <c r="F5" s="24">
-        <f>SUMIFS(Plan!F2:F32,Plan!B2:B32,A5)</f>
+        <f>SUMIFS(Plan!F2:F33,Plan!B2:B33,A5)</f>
         <v/>
       </c>
       <c r="G5" s="25">
@@ -3497,7 +3559,7 @@
         <v>72</v>
       </c>
       <c r="F6" s="24">
-        <f>SUMIFS(Plan!F2:F32,Plan!B2:B32,A6)</f>
+        <f>SUMIFS(Plan!F2:F33,Plan!B2:B33,A6)</f>
         <v/>
       </c>
       <c r="G6" s="25">
@@ -3531,7 +3593,7 @@
         <v>240</v>
       </c>
       <c r="F7" s="24">
-        <f>SUMIFS(Plan!F2:F32,Plan!B2:B32,A7)</f>
+        <f>SUMIFS(Plan!F2:F33,Plan!B2:B33,A7)</f>
         <v/>
       </c>
       <c r="G7" s="25">

--- a/Synapse_Project_Plan_v3.xlsx
+++ b/Synapse_Project_Plan_v3.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Plan" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Milestones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sprint Plan" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Risks &amp; Decisions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks &amp; Decisions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1784,11 +1784,11 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H14" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="17" t="n">
         <v>46188</v>
@@ -1796,14 +1796,16 @@
       <c r="J14" s="17" t="n">
         <v>46199</v>
       </c>
-      <c r="K14" s="17" t="n"/>
+      <c r="K14" s="17" t="n">
+        <v>46192</v>
+      </c>
       <c r="L14" s="14">
         <f>IF(K14="","",IF(K14&lt;=J14,"On-Time","Late"))</f>
         <v/>
       </c>
       <c r="M14" s="15" t="inlineStr">
         <is>
-          <t>NEW. Subscription -&gt; enforced level of access.</t>
+          <t>COMPLETE (2026-06-19 Admin/Auth build) - real JWT login (jose+bcrypt), actor-seam token verification + AUTH_REQUIRED prod gate (enforcement), users+roles + RBAC nav, admin UI. Dev login admin@synapse.local.</t>
         </is>
       </c>
     </row>
@@ -2004,11 +2006,11 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H18" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="17" t="n">
         <v>46188</v>
@@ -2016,14 +2018,16 @@
       <c r="J18" s="17" t="n">
         <v>46199</v>
       </c>
-      <c r="K18" s="17" t="n"/>
+      <c r="K18" s="17" t="n">
+        <v>46192</v>
+      </c>
       <c r="L18" s="14">
         <f>IF(K18="","",IF(K18&lt;=J18,"On-Time","Late"))</f>
         <v/>
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t>Append-only, before/after diff.</t>
+          <t>COMPLETE (2026-06-19 Admin/Auth build) - audit-log write path + Audit Viewer UI; actor/action recorded across privileged routes.</t>
         </is>
       </c>
     </row>
@@ -2278,11 +2282,11 @@
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H23" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="17" t="n">
         <v>46202</v>
@@ -2290,14 +2294,16 @@
       <c r="J23" s="17" t="n">
         <v>46213</v>
       </c>
-      <c r="K23" s="17" t="n"/>
+      <c r="K23" s="17" t="n">
+        <v>46192</v>
+      </c>
       <c r="L23" s="14">
         <f>IF(K23="","",IF(K23&lt;=J23,"On-Time","Late"))</f>
         <v/>
       </c>
       <c r="M23" s="15" t="inlineStr">
         <is>
-          <t>Next-run preview.</t>
+          <t>COMPLETE - SchedulerService.initScheduler wired into hub boot (BullMQ repeatable jobs via upsertJobScheduler); per-connection schedule managed from the Connected page. Cron-builder UI is minimal.</t>
         </is>
       </c>
     </row>
@@ -2332,11 +2338,11 @@
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H24" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="17" t="n">
         <v>46202</v>
@@ -2344,14 +2350,16 @@
       <c r="J24" s="17" t="n">
         <v>46213</v>
       </c>
-      <c r="K24" s="17" t="n"/>
+      <c r="K24" s="17" t="n">
+        <v>46192</v>
+      </c>
       <c r="L24" s="14">
         <f>IF(K24="","",IF(K24&lt;=J24,"On-Time","Late"))</f>
         <v/>
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
-          <t>Existing engine regression.</t>
+          <t>COMPLETE - Jira-&gt;SharePoint moved onto the IntegrationBus (bus-egress cutover) + push-reliability hardening / connection de-dup; delivered via the SharePoint destination with idempotency, retry/backoff and DLQ.</t>
         </is>
       </c>
     </row>
